--- a/data/opleidingsniveau.xlsx
+++ b/data/opleidingsniveau.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E661AA2-01C4-B34E-8452-F04E2FFA91F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96716873-A16C-C04F-B3FF-EBE97670FF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OpleidingsniveauType" sheetId="8" r:id="rId1"/>
+    <sheet name="_customVoc" sheetId="9" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="110">
   <si>
     <t>CODE</t>
   </si>
@@ -325,13 +326,46 @@
   </si>
   <si>
     <t>Secundair volwassenenonderwijs - modules geletterdheid</t>
+  </si>
+  <si>
+    <t>sheetLabel</t>
+  </si>
+  <si>
+    <t>sheetClass</t>
+  </si>
+  <si>
+    <t>columnLabel</t>
+  </si>
+  <si>
+    <t>columnProperty</t>
+  </si>
+  <si>
+    <t>valueDatatype</t>
+  </si>
+  <si>
+    <t>valueClass</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/title</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2001/XMLSchema#string</t>
+  </si>
+  <si>
+    <t>OpleidingsniveauType</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2004/02/skos/core#Concept</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2004/02/skos/core#broader</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -349,6 +383,22 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -432,10 +482,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -453,8 +504,11 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1313,4 +1367,81 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{983D3F0E-8FB3-CB4F-B296-24A5AA4B6571}">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{18EECC8B-6E60-844C-9404-CE27715681C8}"/>
+    <hyperlink ref="E2" r:id="rId2" location="string" xr:uid="{0691F251-E5F9-484F-8E44-53B53745155F}"/>
+    <hyperlink ref="D3" r:id="rId3" location="broader" xr:uid="{38B22130-C8BB-E94A-AEFC-D2922EF7DB55}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/opleidingsniveau.xlsx
+++ b/data/opleidingsniveau.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96716873-A16C-C04F-B3FF-EBE97670FF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5315CE20-21A4-42FC-BCFC-5F3A6637F4BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OpleidingsniveauType" sheetId="8" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="110">
   <si>
     <t>CODE</t>
   </si>
@@ -365,7 +365,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -379,13 +379,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -404,7 +397,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -416,20 +409,8 @@
         <fgColor rgb="FFE0E0E0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCE6F1"/>
-        <bgColor rgb="FFDCE6F1"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -437,56 +418,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF95B3D7"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF95B3D7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF95B3D7"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -494,24 +431,39 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -522,6 +474,33 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0417B50C-3480-4194-8B53-933DDC49C5D1}" name="Table2" displayName="Table2" ref="A1:C49" totalsRowShown="0">
+  <autoFilter ref="A1:C49" xr:uid="{0417B50C-3480-4194-8B53-933DDC49C5D1}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{BBEB7D7E-BF6B-4972-BF59-E6C51AFD171A}" name="CODE"/>
+    <tableColumn id="2" xr3:uid="{86125184-1E97-4325-8E2D-188BA0444BCE}" name="naam"/>
+    <tableColumn id="3" xr3:uid="{06E762D2-A751-4CB4-81E7-1C78E7B74300}" name="isSpecialisatieVan"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{14E599D3-EA9D-445A-B8FD-5B944BBC9043}" name="Table1" displayName="Table1" ref="A1:F3" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:F3" xr:uid="{14E599D3-EA9D-445A-B8FD-5B944BBC9043}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{5245F2C0-A9F8-42ED-AEB9-588408F0D4F8}" name="sheetLabel"/>
+    <tableColumn id="2" xr3:uid="{393A7EC1-3846-483D-B568-BC41B1C0A318}" name="sheetClass"/>
+    <tableColumn id="3" xr3:uid="{A7856318-DC47-49C4-99BA-0DBB293C7B68}" name="columnLabel"/>
+    <tableColumn id="4" xr3:uid="{27EF5EB8-F458-4D5A-95AC-DE173083B37B}" name="columnProperty" dataCellStyle="Hyperlink"/>
+    <tableColumn id="5" xr3:uid="{22149C96-36D8-4639-99D8-F1F554F95174}" name="valueDatatype"/>
+    <tableColumn id="6" xr3:uid="{035509F0-64B9-49E9-958B-FBC69FF36E3D}" name="valueClass"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -847,579 +826,590 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40" style="1" customWidth="1"/>
-    <col min="2" max="2" width="51.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="C2"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="7"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="C3"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="6"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="C4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="7"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="C9"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="6"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="C14"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="7"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+      <c r="C15"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="6"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="C16"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
+      <c r="C19"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="B20" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="6"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+      <c r="C20"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" t="s">
         <v>73</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" t="s">
         <v>77</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="6"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
+      <c r="C28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>32</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" t="s">
         <v>82</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>33</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="6"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
+      <c r="C32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" t="s">
         <v>85</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" t="s">
         <v>86</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="5" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" t="s">
         <v>87</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" t="s">
         <v>91</v>
       </c>
-      <c r="C36" s="6"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="5" t="s">
+      <c r="C36" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" t="s">
         <v>90</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="5" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" t="s">
         <v>89</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="6"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="5" t="s">
+      <c r="C40"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" t="s">
         <v>92</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" t="s">
         <v>94</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="5" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>44</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="7"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
+      <c r="C43" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>45</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="5" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>46</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" t="s">
         <v>96</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" t="s">
         <v>97</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="5" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>48</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" t="s">
         <v>98</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="4" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>49</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" t="s">
         <v>61</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" t="s">
+        <v>84</v>
+      </c>
+      <c r="C49" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C49" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{983D3F0E-8FB3-CB4F-B296-24A5AA4B6571}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="3" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>107</v>
       </c>
@@ -1429,7 +1419,7 @@
       <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="4" t="s">
         <v>109</v>
       </c>
       <c r="F3" t="s">
@@ -1443,5 +1433,8 @@
     <hyperlink ref="D3" r:id="rId3" location="broader" xr:uid="{38B22130-C8BB-E94A-AEFC-D2922EF7DB55}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>